--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487522_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487522_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8173</v>
+        <v>6.7883</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1234</v>
+        <v>6.5063</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3061</v>
+        <v>0.282</v>
       </c>
       <c r="G2" t="n">
         <v>3.1731</v>
@@ -610,13 +610,13 @@
         <v>2.546</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7511</v>
+        <v>-0.7802</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5652</v>
+        <v>-0.1823</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1859</v>
+        <v>-0.5978</v>
       </c>
       <c r="V2" t="n">
         <v>2.0452</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9895</v>
+        <v>4.1617</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3832</v>
+        <v>3.502</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6062</v>
+        <v>0.6597</v>
       </c>
       <c r="G3" t="n">
         <v>0.8845</v>
@@ -688,13 +688,13 @@
         <v>1.7626</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1361</v>
+        <v>0.0362</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0306</v>
+        <v>0.0882</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1055</v>
+        <v>-0.052</v>
       </c>
       <c r="V3" t="n">
         <v>2.6535</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. FALL</t>
+          <t>P. SANJURJO BOTEJARA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4081</v>
+        <v>1.6963</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2832</v>
+        <v>1.6788</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1249</v>
+        <v>0.0175</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4986</v>
+        <v>5.5568</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2902</v>
+        <v>1.8534</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2084</v>
+        <v>3.7034</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3037</v>
+        <v>5.536</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1213</v>
+        <v>2.2575</v>
       </c>
       <c r="L4" t="n">
-        <v>2.1824</v>
+        <v>3.2784</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.8052</v>
+        <v>0.0208</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.8311</v>
+        <v>-0.4041</v>
       </c>
       <c r="O4" t="n">
-        <v>0.026</v>
+        <v>0.4249</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.1128</v>
+        <v>-2.9377</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1543</v>
+        <v>1.9585</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6477</v>
+        <v>-0.0023</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6003</v>
+        <v>0.0794</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0474</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2203</v>
+        <v>-2.8788</v>
       </c>
       <c r="W4" t="n">
-        <v>1.492</v>
+        <v>-0.9988</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2717</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. SANJURJO BOTEJARA</t>
+          <t>K. FALL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0111</v>
+        <v>1.3725</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8866000000000001</v>
+        <v>1.9693</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1245</v>
+        <v>-0.5968</v>
       </c>
       <c r="G5" t="n">
-        <v>5.5568</v>
+        <v>2.4986</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8534</v>
+        <v>0.2902</v>
       </c>
       <c r="I5" t="n">
-        <v>3.7034</v>
+        <v>2.2084</v>
       </c>
       <c r="J5" t="n">
-        <v>5.536</v>
+        <v>4.3037</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2575</v>
+        <v>2.1213</v>
       </c>
       <c r="L5" t="n">
-        <v>3.2784</v>
+        <v>2.1824</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0208</v>
+        <v>-1.8052</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4041</v>
+        <v>-1.8311</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4249</v>
+        <v>0.026</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9377</v>
+        <v>-4.1128</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9585</v>
+        <v>2.1543</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6876</v>
+        <v>0.6121</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7128</v>
+        <v>0.2864</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0252</v>
+        <v>0.3257</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.8788</v>
+        <v>0.2203</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.9988</v>
+        <v>1.492</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.88</v>
+        <v>-1.2717</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MARTINEZ FERREIRO</t>
+          <t>D. WILLIAM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9645</v>
+        <v>1.1046</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3723</v>
+        <v>3.241</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4078</v>
+        <v>-2.1364</v>
       </c>
       <c r="G6" t="n">
-        <v>1.012</v>
+        <v>3.2993</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5727</v>
+        <v>2.3798</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4394</v>
+        <v>0.9195</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5506</v>
+        <v>4.0306</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9799</v>
+        <v>3.9401</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5706</v>
+        <v>0.0905</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5385</v>
+        <v>-0.7312</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4073</v>
+        <v>-1.5603</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1313</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1958</v>
+        <v>0.5875</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1751</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1958</v>
+        <v>1.7626</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2434</v>
+        <v>-0.6245000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1782</v>
+        <v>-0.4982</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.1263</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-2.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.8837</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-3.0415</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. WILLIAM</t>
+          <t>J. MARTINEZ FERREIRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.287</v>
+        <v>1.0714</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6105</v>
+        <v>1.3723</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.3235</v>
+        <v>-0.3009</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2993</v>
+        <v>1.012</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3798</v>
+        <v>0.5727</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9195</v>
+        <v>0.4394</v>
       </c>
       <c r="J7" t="n">
-        <v>4.0306</v>
+        <v>1.5506</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9401</v>
+        <v>0.9799</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0905</v>
+        <v>0.5706</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7312</v>
+        <v>-0.5385</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5603</v>
+        <v>-0.4073</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8290999999999999</v>
+        <v>-0.1313</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5875</v>
+        <v>0.1958</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1751</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7626</v>
+        <v>0.1958</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.442</v>
+        <v>-0.1364</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1286</v>
+        <v>-0.1782</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3134</v>
+        <v>0.0418</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1578</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8837</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.0415</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0783</v>
+        <v>-2.5176</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.6446</v>
+        <v>-3.7898</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5663</v>
+        <v>1.2722</v>
       </c>
       <c r="G8" t="n">
         <v>-2.4658</v>
@@ -1078,13 +1078,13 @@
         <v>1.7626</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7126</v>
+        <v>0.2733</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0306</v>
+        <v>-0.1759</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7432</v>
+        <v>0.4492</v>
       </c>
       <c r="V8" t="n">
         <v>0.06660000000000001</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.6809</v>
+        <v>-3.1762</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.5352</v>
+        <v>-3.2711</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1457</v>
+        <v>0.0949</v>
       </c>
       <c r="G9" t="n">
         <v>-1.467</v>
@@ -1156,13 +1156,13 @@
         <v>0.9792</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2347</v>
+        <v>-0.73</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7128</v>
+        <v>-0.4488</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5219</v>
+        <v>-0.2813</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8434</v>
+        <v>-3.7351</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2852</v>
+        <v>-2.1234</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5582</v>
+        <v>-1.6117</v>
       </c>
       <c r="G10" t="n">
         <v>-1.0076</v>
@@ -1234,13 +1234,13 @@
         <v>0.5875</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0678</v>
+        <v>-0.9595</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.594</v>
+        <v>-0.4323</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4738</v>
+        <v>-0.5273</v>
       </c>
       <c r="V10" t="n">
         <v>-0.397</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>5.874900000000001</v>
+        <v>6.765899999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>8.194200000000002</v>
+        <v>9.085400000000002</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3194</v>
+        <v>-2.3195</v>
       </c>
       <c r="G11" t="n">
         <v>11.4839</v>
@@ -1312,13 +1312,13 @@
         <v>13.7091</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.2024</v>
+        <v>-2.3113</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.3525</v>
+        <v>-1.4617</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8498999999999999</v>
+        <v>-0.8497</v>
       </c>
       <c r="V11" t="n">
         <v>-0.4479999999999993</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.9398</v>
+        <v>3.6503</v>
       </c>
       <c r="E12" t="n">
-        <v>5.1991</v>
+        <v>5.0967</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2593</v>
+        <v>-1.4464</v>
       </c>
       <c r="G12" t="n">
         <v>2.7322</v>
@@ -1390,13 +1390,13 @@
         <v>2.9377</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9909</v>
+        <v>0.7015</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4076</v>
+        <v>0.3052</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5834</v>
+        <v>0.3963</v>
       </c>
       <c r="V12" t="n">
         <v>0.6083</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. RUANO MARTINEZ</t>
+          <t>C. DARRIBA VAZQUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4396</v>
+        <v>2.0556</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3547</v>
+        <v>3.8976</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0849</v>
+        <v>-1.842</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1949</v>
+        <v>0.8124</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1133</v>
+        <v>1.1453</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.3081</v>
+        <v>-0.333</v>
       </c>
       <c r="J13" t="n">
-        <v>2.0874</v>
+        <v>3.5039</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6079</v>
+        <v>2.7765</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5206</v>
+        <v>0.7275</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.2822</v>
+        <v>-2.6916</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4947</v>
+        <v>-1.6311</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.7875</v>
+        <v>-1.0604</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5668</v>
+        <v>1.3709</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.1958</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7626</v>
+        <v>1.5668</v>
       </c>
       <c r="S13" t="n">
-        <v>2.676</v>
+        <v>0.5381</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7962</v>
+        <v>0.0388</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8799</v>
+        <v>0.4993</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6083</v>
+        <v>-0.6659</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.3329</v>
+        <v>0.5507</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2754</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. DARRIBA VAZQUEZ</t>
+          <t>M. RUANO MARTINEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2323</v>
+        <v>1.9443</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1813</v>
+        <v>2.1267</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.949</v>
+        <v>-0.1824</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8124</v>
+        <v>-0.1949</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1453</v>
+        <v>1.1133</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.333</v>
+        <v>-1.3081</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5039</v>
+        <v>2.0874</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7765</v>
+        <v>2.6079</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7275</v>
+        <v>-0.5206</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.6916</v>
+        <v>-2.2822</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.6311</v>
+        <v>-1.4947</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0604</v>
+        <v>-0.7875</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3709</v>
+        <v>1.5668</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.1958</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5668</v>
+        <v>1.7626</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2851</v>
+        <v>1.1807</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6775</v>
+        <v>0.5681</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3924</v>
+        <v>0.6125</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6659</v>
+        <v>-0.6083</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5507</v>
+        <v>-0.3329</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7845</v>
+        <v>1.3809</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3102</v>
+        <v>0.7195</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4743</v>
+        <v>0.6614</v>
       </c>
       <c r="G15" t="n">
         <v>-3.2732</v>
@@ -1624,13 +1624,13 @@
         <v>2.3502</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0589</v>
+        <v>0.6553</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4288</v>
+        <v>-0.0194</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4876</v>
+        <v>0.6747</v>
       </c>
       <c r="V15" t="n">
         <v>2.8237</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1957</v>
+        <v>0.0445</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8657</v>
+        <v>0.661</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6699000000000001</v>
+        <v>-0.6165</v>
       </c>
       <c r="G16" t="n">
         <v>0.791</v>
@@ -1702,13 +1702,13 @@
         <v>1.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3679</v>
+        <v>0.2167</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.317</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1537</v>
+        <v>-0.1003</v>
       </c>
       <c r="V16" t="n">
         <v>-1.159</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.5978</v>
+        <v>-1.5222</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7017</v>
+        <v>-0.5994</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.896</v>
+        <v>-0.9228</v>
       </c>
       <c r="G17" t="n">
         <v>-1.2068</v>
@@ -1780,13 +1780,13 @@
         <v>0.5875</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0949</v>
+        <v>-0.0193</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1012</v>
+        <v>0.0012</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0063</v>
+        <v>-0.0204</v>
       </c>
       <c r="V17" t="n">
         <v>-0.8837</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.4652</v>
+        <v>-3.2605</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5218</v>
+        <v>-2.3172</v>
       </c>
       <c r="F18" t="n">
         <v>-0.9433</v>
@@ -1858,10 +1858,10 @@
         <v>1.9585</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1123</v>
+        <v>0.317</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3517</v>
+        <v>-0.147</v>
       </c>
       <c r="U18" t="n">
         <v>0.464</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.7739</v>
+        <v>-4.5959</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8554</v>
+        <v>-2.6507</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9185</v>
+        <v>-1.9452</v>
       </c>
       <c r="G19" t="n">
         <v>-2.934</v>
@@ -1936,13 +1936,13 @@
         <v>0.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4689</v>
+        <v>-0.291</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3982</v>
+        <v>-0.1935</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0708</v>
+        <v>-0.0975</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.6299</v>
+        <v>-5.5719</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.5125</v>
+        <v>-4.6148</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1175</v>
+        <v>-0.9571</v>
       </c>
       <c r="G20" t="n">
         <v>-3.1042</v>
@@ -2014,13 +2014,13 @@
         <v>2.546</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1548</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>0.08169999999999999</v>
+        <v>-0.0206</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2365</v>
+        <v>-0.0762</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6083</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.874900000000001</v>
+        <v>-5.874900000000003</v>
       </c>
       <c r="E21" t="n">
-        <v>2.319599999999999</v>
+        <v>2.319400000000001</v>
       </c>
       <c r="F21" t="n">
         <v>-8.1943</v>
@@ -2095,10 +2095,10 @@
         <v>3.2023</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8498000000000002</v>
+        <v>0.8498000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>2.3526</v>
+        <v>2.3524</v>
       </c>
       <c r="V21" t="n">
         <v>0.4480000000000001</v>
